--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción halpha 2024, 2025 y 2026.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción halpha 2024, 2025 y 2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Septiembre 06-2025</t>
+          <t>Julio 24-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6563.167</v>
+        <v>6562.853</v>
       </c>
       <c r="D14" t="n">
-        <v>5.4e-05</v>
+        <v>6e-06</v>
       </c>
       <c r="E14" t="n">
-        <v>16.2206</v>
+        <v>1.8737</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7306</v>
+        <v>0.6818</v>
       </c>
       <c r="G14" t="n">
-        <v>1.115</v>
+        <v>1.214</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0315</v>
+        <v>1.0234</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Julio 22-2026</t>
+          <t>Julio 27-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -872,28 +872,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6562.988</v>
+        <v>6562.889</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7e-05</v>
+        <v>1.2e-05</v>
       </c>
       <c r="E15" t="n">
-        <v>8.037800000000001</v>
+        <v>3.5257</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7635</v>
+        <v>0.6597</v>
       </c>
       <c r="G15" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0606</v>
+        <v>0.9416</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Julio 24-2026</t>
+          <t>Agosto 06-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -902,28 +902,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6562.853</v>
+        <v>6562.842</v>
       </c>
       <c r="D16" t="n">
-        <v>6e-06</v>
+        <v>5e-06</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8737</v>
+        <v>1.3536</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6818</v>
+        <v>0.716</v>
       </c>
       <c r="G16" t="n">
-        <v>1.214</v>
+        <v>1.293</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0234</v>
+        <v>1.128</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Julio 27-2026</t>
+          <t>Agosto 10-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,28 +932,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6562.889</v>
+        <v>6562.873</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2e-05</v>
+        <v>9e-06</v>
       </c>
       <c r="E17" t="n">
-        <v>3.5257</v>
+        <v>2.7949</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6597</v>
+        <v>0.7371</v>
       </c>
       <c r="G17" t="n">
-        <v>1.13</v>
+        <v>1.307</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9416</v>
+        <v>1.1687</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Agosto 06-2026</t>
+          <t>Agosto 13-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -962,28 +962,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6562.842</v>
+        <v>6562.875</v>
       </c>
       <c r="D18" t="n">
-        <v>5e-06</v>
+        <v>1e-05</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3536</v>
+        <v>2.8908</v>
       </c>
       <c r="F18" t="n">
-        <v>0.716</v>
+        <v>0.7149</v>
       </c>
       <c r="G18" t="n">
-        <v>1.293</v>
+        <v>1.311</v>
       </c>
       <c r="H18" t="n">
-        <v>1.128</v>
+        <v>1.1508</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Agosto 10-2026</t>
+          <t>Agosto 28-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -992,28 +992,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6562.873</v>
+        <v>6562.98</v>
       </c>
       <c r="D19" t="n">
-        <v>9e-06</v>
+        <v>2.6e-05</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7949</v>
+        <v>7.66</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7371</v>
+        <v>0.7614</v>
       </c>
       <c r="G19" t="n">
-        <v>1.307</v>
+        <v>1.282</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1687</v>
+        <v>1.077</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Agosto 13-2026</t>
+          <t>Septiembre 07-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1022,111 +1022,21 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6562.875</v>
+        <v>6562.949</v>
       </c>
       <c r="D20" t="n">
-        <v>1e-05</v>
+        <v>2.1e-05</v>
       </c>
       <c r="E20" t="n">
-        <v>2.8908</v>
+        <v>6.2449</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7149</v>
+        <v>0.7348</v>
       </c>
       <c r="G20" t="n">
-        <v>1.311</v>
+        <v>1.307</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1508</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Agosto 26-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Absorción Hα</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>6563.11</v>
-      </c>
-      <c r="D21" t="n">
-        <v>4.5e-05</v>
-      </c>
-      <c r="E21" t="n">
-        <v>13.6078</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.8577</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.156</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1.1613</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Agosto 28-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Absorción Hα</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>6562.98</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2.6e-05</v>
-      </c>
-      <c r="E22" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.7614</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1.282</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.077</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Septiembre 07-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Absorción Hα</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>6562.949</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.1e-05</v>
-      </c>
-      <c r="E23" t="n">
-        <v>6.2449</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.7348</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1.307</v>
-      </c>
-      <c r="H23" t="n">
         <v>1.0736</v>
       </c>
     </row>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción halpha 2024, 2025 y 2026.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción halpha 2024, 2025 y 2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,20 +451,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Velocidad [km/s]</t>
+          <t>Velocidad obs. [km/s]</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Velocidad heliocéntrica [km/s]</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Profundidad / Altura</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>FWHM [Å]</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>EW [Å]</t>
         </is>
@@ -488,15 +493,18 @@
         <v>1.4e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2427</v>
+        <v>4.24</v>
       </c>
       <c r="F2" t="n">
+        <v>-14.41</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.9122</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>1.059</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>1.1795</v>
       </c>
     </row>
@@ -518,15 +526,18 @@
         <v>3.4e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>10.3394</v>
+        <v>10.34</v>
       </c>
       <c r="F3" t="n">
+        <v>-12.18</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.6215000000000001</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>0.875</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>0.6232</v>
       </c>
     </row>
@@ -548,15 +559,18 @@
         <v>3.2e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>9.7233</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="F4" t="n">
+        <v>-18.62</v>
+      </c>
+      <c r="G4" t="n">
         <v>0.9089</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>1.164</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>1.309</v>
       </c>
     </row>
@@ -578,15 +592,18 @@
         <v>3.5e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>10.6416</v>
+        <v>10.64</v>
       </c>
       <c r="F5" t="n">
+        <v>-18.71</v>
+      </c>
+      <c r="G5" t="n">
         <v>0.9061</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>1.208</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>1.2492</v>
       </c>
     </row>
@@ -608,15 +625,18 @@
         <v>4.5e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>13.357</v>
+        <v>13.36</v>
       </c>
       <c r="F6" t="n">
+        <v>-16.21</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.7659</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>1.175</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>1.1158</v>
       </c>
     </row>
@@ -638,15 +658,18 @@
         <v>4.4e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>13.2045</v>
+        <v>13.2</v>
       </c>
       <c r="F7" t="n">
+        <v>-15.18</v>
+      </c>
+      <c r="G7" t="n">
         <v>0.6959</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>1.095</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>0.915</v>
       </c>
     </row>
@@ -668,15 +691,18 @@
         <v>2.8e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>8.5372</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="F8" t="n">
+        <v>-18.95</v>
+      </c>
+      <c r="G8" t="n">
         <v>0.7731</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>1.268</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>1.1841</v>
       </c>
     </row>
@@ -698,15 +724,18 @@
         <v>3e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>8.9337</v>
+        <v>8.93</v>
       </c>
       <c r="F9" t="n">
+        <v>-17.09</v>
+      </c>
+      <c r="G9" t="n">
         <v>0.7266</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>1.234</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>1.069</v>
       </c>
     </row>
@@ -728,15 +757,18 @@
         <v>2.6e-05</v>
       </c>
       <c r="E10" t="n">
-        <v>7.9443</v>
+        <v>7.94</v>
       </c>
       <c r="F10" t="n">
+        <v>-15.17</v>
+      </c>
+      <c r="G10" t="n">
         <v>0.825</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>1.177</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>1.2804</v>
       </c>
     </row>
@@ -758,15 +790,18 @@
         <v>1.9e-05</v>
       </c>
       <c r="E11" t="n">
-        <v>5.8222</v>
+        <v>5.82</v>
       </c>
       <c r="F11" t="n">
+        <v>-15.23</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.7957</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>1.154</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>1.1765</v>
       </c>
     </row>
@@ -788,15 +823,18 @@
         <v>9e-06</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7643</v>
+        <v>2.76</v>
       </c>
       <c r="F12" t="n">
+        <v>-17.96</v>
+      </c>
+      <c r="G12" t="n">
         <v>0.6762</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>1.252</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>1.0153</v>
       </c>
     </row>
@@ -818,15 +856,18 @@
         <v>1e-05</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0169</v>
+        <v>3.02</v>
       </c>
       <c r="F13" t="n">
+        <v>-15.41</v>
+      </c>
+      <c r="G13" t="n">
         <v>0.641</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>1.231</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>1.0231</v>
       </c>
     </row>
@@ -848,15 +889,18 @@
         <v>6e-06</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8737</v>
+        <v>1.87</v>
       </c>
       <c r="F14" t="n">
+        <v>-21.26</v>
+      </c>
+      <c r="G14" t="n">
         <v>0.6818</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>1.214</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>1.0234</v>
       </c>
     </row>
@@ -878,15 +922,18 @@
         <v>1.2e-05</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5257</v>
+        <v>3.53</v>
       </c>
       <c r="F15" t="n">
+        <v>-20.4</v>
+      </c>
+      <c r="G15" t="n">
         <v>0.6597</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>1.13</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>0.9416</v>
       </c>
     </row>
@@ -908,15 +955,18 @@
         <v>5e-06</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3536</v>
+        <v>1.35</v>
       </c>
       <c r="F16" t="n">
+        <v>-25.15</v>
+      </c>
+      <c r="G16" t="n">
         <v>0.716</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>1.293</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>1.128</v>
       </c>
     </row>
@@ -938,15 +988,18 @@
         <v>9e-06</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7949</v>
+        <v>2.79</v>
       </c>
       <c r="F17" t="n">
+        <v>-24.86</v>
+      </c>
+      <c r="G17" t="n">
         <v>0.7371</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>1.307</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>1.1687</v>
       </c>
     </row>
@@ -968,15 +1021,18 @@
         <v>1e-05</v>
       </c>
       <c r="E18" t="n">
-        <v>2.8908</v>
+        <v>2.89</v>
       </c>
       <c r="F18" t="n">
+        <v>-24.93</v>
+      </c>
+      <c r="G18" t="n">
         <v>0.7149</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>1.311</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>1.1508</v>
       </c>
     </row>
@@ -1001,12 +1057,15 @@
         <v>7.66</v>
       </c>
       <c r="F19" t="n">
+        <v>-21.83</v>
+      </c>
+      <c r="G19" t="n">
         <v>0.7614</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>1.282</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>1.077</v>
       </c>
     </row>
@@ -1028,16 +1087,118 @@
         <v>2.1e-05</v>
       </c>
       <c r="E20" t="n">
-        <v>6.2449</v>
+        <v>6.24</v>
       </c>
       <c r="F20" t="n">
+        <v>-23.27</v>
+      </c>
+      <c r="G20" t="n">
         <v>0.7348</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>1.307</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>1.0736</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Septiembre 14-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Absorción Hα</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>6562.933</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.8e-05</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-23.45</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7742</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.307</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.1705</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Septiembre 21-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Absorción Hα</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>6562.634</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-2.7e-05</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-8.140000000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-36.35</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.8189</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.6087</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Septiembre 29-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Absorción Hα</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>6562.752</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-9e-06</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-2.76</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-29.34</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.8161</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.538</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción halpha 2024, 2025 y 2026.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción halpha 2024, 2025 y 2026.xlsx
@@ -487,25 +487,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6562.905</v>
+        <v>6562.913</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4e-05</v>
+        <v>1.5e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>4.24</v>
+        <v>4.61</v>
       </c>
       <c r="F2" t="n">
-        <v>-14.41</v>
+        <v>-14.04</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9122</v>
+        <v>0.7577</v>
       </c>
       <c r="H2" t="n">
-        <v>1.059</v>
+        <v>1.012</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1795</v>
+        <v>0.9297</v>
       </c>
     </row>
     <row r="3">
@@ -520,25 +520,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6563.038</v>
+        <v>6563.039</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4e-05</v>
+        <v>3.5e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>10.34</v>
+        <v>10.35</v>
       </c>
       <c r="F3" t="n">
-        <v>-12.18</v>
+        <v>-12.17</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.6212</v>
       </c>
       <c r="H3" t="n">
-        <v>0.875</v>
+        <v>0.874</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6232</v>
+        <v>0.6226</v>
       </c>
     </row>
     <row r="4">
@@ -553,25 +553,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6563.025</v>
+        <v>6563.101</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2e-05</v>
+        <v>4.4e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>9.720000000000001</v>
+        <v>13.19</v>
       </c>
       <c r="F4" t="n">
-        <v>-18.62</v>
+        <v>-15.15</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9089</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>1.164</v>
+        <v>1.09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.309</v>
+        <v>0.9929</v>
       </c>
     </row>
     <row r="5">
@@ -586,25 +586,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6563.045</v>
+        <v>6563.069</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5e-05</v>
+        <v>3.9e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>10.64</v>
+        <v>11.76</v>
       </c>
       <c r="F5" t="n">
-        <v>-18.71</v>
+        <v>-17.59</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9061</v>
+        <v>0.8393</v>
       </c>
       <c r="H5" t="n">
-        <v>1.208</v>
+        <v>1.182</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2492</v>
+        <v>1.1297</v>
       </c>
     </row>
     <row r="6">
@@ -619,25 +619,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6563.104</v>
+        <v>6563.15</v>
       </c>
       <c r="D6" t="n">
-        <v>4.5e-05</v>
+        <v>5.1e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>13.36</v>
+        <v>15.42</v>
       </c>
       <c r="F6" t="n">
-        <v>-16.21</v>
+        <v>-14.15</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7659</v>
+        <v>0.6791</v>
       </c>
       <c r="H6" t="n">
-        <v>1.175</v>
+        <v>1.078</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1158</v>
+        <v>0.9015</v>
       </c>
     </row>
     <row r="7">
@@ -652,25 +652,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6563.101</v>
+        <v>6563.129</v>
       </c>
       <c r="D7" t="n">
-        <v>4.4e-05</v>
+        <v>4.8e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>13.2</v>
+        <v>14.49</v>
       </c>
       <c r="F7" t="n">
-        <v>-15.18</v>
+        <v>-13.89</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6959</v>
+        <v>0.6444</v>
       </c>
       <c r="H7" t="n">
-        <v>1.095</v>
+        <v>1.072</v>
       </c>
       <c r="I7" t="n">
-        <v>0.915</v>
+        <v>0.8299</v>
       </c>
     </row>
     <row r="8">
@@ -685,25 +685,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6562.999</v>
+        <v>6563.039</v>
       </c>
       <c r="D8" t="n">
-        <v>2.8e-05</v>
+        <v>3.5e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>8.539999999999999</v>
+        <v>10.38</v>
       </c>
       <c r="F8" t="n">
-        <v>-18.95</v>
+        <v>-17.11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7731</v>
+        <v>0.7056</v>
       </c>
       <c r="H8" t="n">
-        <v>1.268</v>
+        <v>1.246</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1841</v>
+        <v>1.062</v>
       </c>
     </row>
     <row r="9">
@@ -718,25 +718,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6563.008</v>
+        <v>6563.027</v>
       </c>
       <c r="D9" t="n">
-        <v>3e-05</v>
+        <v>3.3e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>8.93</v>
+        <v>9.83</v>
       </c>
       <c r="F9" t="n">
-        <v>-17.09</v>
+        <v>-16.19</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7266</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>1.234</v>
+        <v>1.226</v>
       </c>
       <c r="I9" t="n">
-        <v>1.069</v>
+        <v>1.0146</v>
       </c>
     </row>
     <row r="10">
@@ -751,25 +751,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6562.986</v>
+        <v>6562.989</v>
       </c>
       <c r="D10" t="n">
-        <v>2.6e-05</v>
+        <v>2.7e-05</v>
       </c>
       <c r="E10" t="n">
-        <v>7.94</v>
+        <v>8.09</v>
       </c>
       <c r="F10" t="n">
-        <v>-15.17</v>
+        <v>-15.02</v>
       </c>
       <c r="G10" t="n">
-        <v>0.825</v>
+        <v>0.7983</v>
       </c>
       <c r="H10" t="n">
-        <v>1.177</v>
+        <v>1.143</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2804</v>
+        <v>1.1694</v>
       </c>
     </row>
     <row r="11">
@@ -784,25 +784,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6562.939</v>
+        <v>6562.919</v>
       </c>
       <c r="D11" t="n">
-        <v>1.9e-05</v>
+        <v>1.6e-05</v>
       </c>
       <c r="E11" t="n">
-        <v>5.82</v>
+        <v>4.89</v>
       </c>
       <c r="F11" t="n">
-        <v>-15.23</v>
+        <v>-16.16</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7957</v>
+        <v>0.8025</v>
       </c>
       <c r="H11" t="n">
-        <v>1.154</v>
+        <v>1.157</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1765</v>
+        <v>1.1408</v>
       </c>
     </row>
     <row r="12">
@@ -817,25 +817,25 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6562.873</v>
+        <v>6562.908</v>
       </c>
       <c r="D12" t="n">
-        <v>9e-06</v>
+        <v>1.5e-05</v>
       </c>
       <c r="E12" t="n">
-        <v>2.76</v>
+        <v>4.37</v>
       </c>
       <c r="F12" t="n">
-        <v>-17.96</v>
+        <v>-16.35</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6762</v>
+        <v>0.6516</v>
       </c>
       <c r="H12" t="n">
-        <v>1.252</v>
+        <v>1.206</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0153</v>
+        <v>0.9522</v>
       </c>
     </row>
     <row r="13">
@@ -850,25 +850,25 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6562.878</v>
+        <v>6562.735</v>
       </c>
       <c r="D13" t="n">
-        <v>1e-05</v>
+        <v>-1.2e-05</v>
       </c>
       <c r="E13" t="n">
-        <v>3.02</v>
+        <v>-3.51</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.41</v>
+        <v>-21.94</v>
       </c>
       <c r="G13" t="n">
-        <v>0.641</v>
+        <v>0.657</v>
       </c>
       <c r="H13" t="n">
-        <v>1.231</v>
+        <v>1.531</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0231</v>
+        <v>1.1751</v>
       </c>
     </row>
     <row r="14">
@@ -883,25 +883,25 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6562.853</v>
+        <v>6562.864</v>
       </c>
       <c r="D14" t="n">
-        <v>6e-06</v>
+        <v>8e-06</v>
       </c>
       <c r="E14" t="n">
-        <v>1.87</v>
+        <v>2.39</v>
       </c>
       <c r="F14" t="n">
-        <v>-21.26</v>
+        <v>-20.74</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6818</v>
+        <v>0.6723</v>
       </c>
       <c r="H14" t="n">
-        <v>1.214</v>
+        <v>1.2</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0234</v>
+        <v>0.9969</v>
       </c>
     </row>
     <row r="15">
@@ -928,13 +928,13 @@
         <v>-20.4</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6597</v>
+        <v>0.6605</v>
       </c>
       <c r="H15" t="n">
         <v>1.13</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9416</v>
+        <v>0.9446</v>
       </c>
     </row>
     <row r="16">
@@ -949,25 +949,25 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6562.842</v>
+        <v>6562.95</v>
       </c>
       <c r="D16" t="n">
-        <v>5e-06</v>
+        <v>2.1e-05</v>
       </c>
       <c r="E16" t="n">
-        <v>1.35</v>
+        <v>6.3</v>
       </c>
       <c r="F16" t="n">
-        <v>-25.15</v>
+        <v>-20.2</v>
       </c>
       <c r="G16" t="n">
-        <v>0.716</v>
+        <v>0.6398</v>
       </c>
       <c r="H16" t="n">
-        <v>1.293</v>
+        <v>1.174</v>
       </c>
       <c r="I16" t="n">
-        <v>1.128</v>
+        <v>0.9154</v>
       </c>
     </row>
     <row r="17">
@@ -982,25 +982,25 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6562.873</v>
+        <v>6562.93</v>
       </c>
       <c r="D17" t="n">
-        <v>9e-06</v>
+        <v>1.8e-05</v>
       </c>
       <c r="E17" t="n">
-        <v>2.79</v>
+        <v>5.41</v>
       </c>
       <c r="F17" t="n">
-        <v>-24.86</v>
+        <v>-22.24</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7371</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>1.307</v>
+        <v>1.248</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1687</v>
+        <v>1.0301</v>
       </c>
     </row>
     <row r="18">
@@ -1015,25 +1015,25 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6562.875</v>
+        <v>6562.96</v>
       </c>
       <c r="D18" t="n">
-        <v>1e-05</v>
+        <v>2.3e-05</v>
       </c>
       <c r="E18" t="n">
-        <v>2.89</v>
+        <v>6.76</v>
       </c>
       <c r="F18" t="n">
-        <v>-24.93</v>
+        <v>-21.06</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7149</v>
+        <v>0.6544</v>
       </c>
       <c r="H18" t="n">
-        <v>1.311</v>
+        <v>1.203</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1508</v>
+        <v>0.9794</v>
       </c>
     </row>
     <row r="19">
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6562.98</v>
+        <v>6562.994</v>
       </c>
       <c r="D19" t="n">
-        <v>2.6e-05</v>
+        <v>2.8e-05</v>
       </c>
       <c r="E19" t="n">
-        <v>7.66</v>
+        <v>8.31</v>
       </c>
       <c r="F19" t="n">
-        <v>-21.83</v>
+        <v>-21.18</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7614</v>
+        <v>0.7407</v>
       </c>
       <c r="H19" t="n">
-        <v>1.282</v>
+        <v>1.259</v>
       </c>
       <c r="I19" t="n">
-        <v>1.077</v>
+        <v>1.0243</v>
       </c>
     </row>
     <row r="20">
@@ -1081,25 +1081,25 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6562.949</v>
+        <v>6562.939</v>
       </c>
       <c r="D20" t="n">
-        <v>2.1e-05</v>
+        <v>1.9e-05</v>
       </c>
       <c r="E20" t="n">
-        <v>6.24</v>
+        <v>5.8</v>
       </c>
       <c r="F20" t="n">
-        <v>-23.27</v>
+        <v>-23.71</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7348</v>
+        <v>0.7325</v>
       </c>
       <c r="H20" t="n">
-        <v>1.307</v>
+        <v>1.324</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0736</v>
+        <v>1.0691</v>
       </c>
     </row>
     <row r="21">
@@ -1114,25 +1114,25 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6562.933</v>
+        <v>6562.944</v>
       </c>
       <c r="D21" t="n">
-        <v>1.8e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="E21" t="n">
-        <v>5.51</v>
+        <v>6.01</v>
       </c>
       <c r="F21" t="n">
-        <v>-23.45</v>
+        <v>-22.95</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7742</v>
+        <v>0.716</v>
       </c>
       <c r="H21" t="n">
-        <v>1.307</v>
+        <v>1.297</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1705</v>
+        <v>1.0139</v>
       </c>
     </row>
     <row r="22">
@@ -1165,7 +1165,7 @@
         <v>1.818</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6087</v>
+        <v>1.6089</v>
       </c>
     </row>
     <row r="23">
@@ -1180,25 +1180,25 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6562.752</v>
+        <v>6562.719</v>
       </c>
       <c r="D23" t="n">
-        <v>-9e-06</v>
+        <v>-1.4e-05</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.76</v>
+        <v>-4.23</v>
       </c>
       <c r="F23" t="n">
-        <v>-29.34</v>
+        <v>-30.81</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8161</v>
+        <v>0.7935</v>
       </c>
       <c r="H23" t="n">
-        <v>1.538</v>
+        <v>1.612</v>
       </c>
       <c r="I23" t="n">
-        <v>1.39</v>
+        <v>1.3921</v>
       </c>
     </row>
   </sheetData>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción halpha 2024, 2025 y 2026.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción halpha 2024, 2025 y 2026.xlsx
@@ -489,8 +489,10 @@
       <c r="C2" t="n">
         <v>6562.913</v>
       </c>
-      <c r="D2" t="n">
-        <v>1.5e-05</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.5e-05</t>
+        </is>
       </c>
       <c r="E2" t="n">
         <v>4.61</v>
@@ -499,13 +501,13 @@
         <v>-14.04</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7577</v>
+        <v>0.76</v>
       </c>
       <c r="H2" t="n">
-        <v>1.012</v>
+        <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9297</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="3">
@@ -522,8 +524,10 @@
       <c r="C3" t="n">
         <v>6563.039</v>
       </c>
-      <c r="D3" t="n">
-        <v>3.5e-05</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3.5e-05</t>
+        </is>
       </c>
       <c r="E3" t="n">
         <v>10.35</v>
@@ -532,13 +536,13 @@
         <v>-12.17</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6212</v>
+        <v>0.62</v>
       </c>
       <c r="H3" t="n">
-        <v>0.874</v>
+        <v>0.87</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6226</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="4">
@@ -555,8 +559,10 @@
       <c r="C4" t="n">
         <v>6563.101</v>
       </c>
-      <c r="D4" t="n">
-        <v>4.4e-05</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4.4e-05</t>
+        </is>
       </c>
       <c r="E4" t="n">
         <v>13.19</v>
@@ -565,13 +571,13 @@
         <v>-15.15</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="H4" t="n">
         <v>1.09</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9929</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="5">
@@ -588,8 +594,10 @@
       <c r="C5" t="n">
         <v>6563.069</v>
       </c>
-      <c r="D5" t="n">
-        <v>3.9e-05</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3.9e-05</t>
+        </is>
       </c>
       <c r="E5" t="n">
         <v>11.76</v>
@@ -598,13 +606,13 @@
         <v>-17.59</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8393</v>
+        <v>0.84</v>
       </c>
       <c r="H5" t="n">
-        <v>1.182</v>
+        <v>1.18</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1297</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="6">
@@ -621,8 +629,10 @@
       <c r="C6" t="n">
         <v>6563.15</v>
       </c>
-      <c r="D6" t="n">
-        <v>5.1e-05</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5.1e-05</t>
+        </is>
       </c>
       <c r="E6" t="n">
         <v>15.42</v>
@@ -631,13 +641,13 @@
         <v>-14.15</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6791</v>
+        <v>0.68</v>
       </c>
       <c r="H6" t="n">
-        <v>1.078</v>
+        <v>1.08</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9015</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7">
@@ -654,8 +664,10 @@
       <c r="C7" t="n">
         <v>6563.129</v>
       </c>
-      <c r="D7" t="n">
-        <v>4.8e-05</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4.8e-05</t>
+        </is>
       </c>
       <c r="E7" t="n">
         <v>14.49</v>
@@ -664,13 +676,13 @@
         <v>-13.89</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6444</v>
+        <v>0.64</v>
       </c>
       <c r="H7" t="n">
-        <v>1.072</v>
+        <v>1.07</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8299</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="8">
@@ -687,8 +699,10 @@
       <c r="C8" t="n">
         <v>6563.039</v>
       </c>
-      <c r="D8" t="n">
-        <v>3.5e-05</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3.5e-05</t>
+        </is>
       </c>
       <c r="E8" t="n">
         <v>10.38</v>
@@ -697,13 +711,13 @@
         <v>-17.11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7056</v>
+        <v>0.71</v>
       </c>
       <c r="H8" t="n">
-        <v>1.246</v>
+        <v>1.25</v>
       </c>
       <c r="I8" t="n">
-        <v>1.062</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="9">
@@ -720,8 +734,10 @@
       <c r="C9" t="n">
         <v>6563.027</v>
       </c>
-      <c r="D9" t="n">
-        <v>3.3e-05</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3.3e-05</t>
+        </is>
       </c>
       <c r="E9" t="n">
         <v>9.83</v>
@@ -730,13 +746,13 @@
         <v>-16.19</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>1.226</v>
+        <v>1.23</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0146</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="10">
@@ -753,8 +769,10 @@
       <c r="C10" t="n">
         <v>6562.989</v>
       </c>
-      <c r="D10" t="n">
-        <v>2.7e-05</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2.7e-05</t>
+        </is>
       </c>
       <c r="E10" t="n">
         <v>8.09</v>
@@ -763,13 +781,13 @@
         <v>-15.02</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7983</v>
+        <v>0.8</v>
       </c>
       <c r="H10" t="n">
-        <v>1.143</v>
+        <v>1.14</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1694</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="11">
@@ -786,8 +804,10 @@
       <c r="C11" t="n">
         <v>6562.919</v>
       </c>
-      <c r="D11" t="n">
-        <v>1.6e-05</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1.6e-05</t>
+        </is>
       </c>
       <c r="E11" t="n">
         <v>4.89</v>
@@ -796,13 +816,13 @@
         <v>-16.16</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8025</v>
+        <v>0.8</v>
       </c>
       <c r="H11" t="n">
-        <v>1.157</v>
+        <v>1.16</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1408</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="12">
@@ -819,8 +839,10 @@
       <c r="C12" t="n">
         <v>6562.908</v>
       </c>
-      <c r="D12" t="n">
-        <v>1.5e-05</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.5e-05</t>
+        </is>
       </c>
       <c r="E12" t="n">
         <v>4.37</v>
@@ -829,13 +851,13 @@
         <v>-16.35</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6516</v>
+        <v>0.65</v>
       </c>
       <c r="H12" t="n">
-        <v>1.206</v>
+        <v>1.21</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9522</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="13">
@@ -852,8 +874,10 @@
       <c r="C13" t="n">
         <v>6562.735</v>
       </c>
-      <c r="D13" t="n">
-        <v>-1.2e-05</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-1.2e-05</t>
+        </is>
       </c>
       <c r="E13" t="n">
         <v>-3.51</v>
@@ -862,13 +886,13 @@
         <v>-21.94</v>
       </c>
       <c r="G13" t="n">
-        <v>0.657</v>
+        <v>0.66</v>
       </c>
       <c r="H13" t="n">
-        <v>1.531</v>
+        <v>1.53</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1751</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="14">
@@ -885,8 +909,10 @@
       <c r="C14" t="n">
         <v>6562.864</v>
       </c>
-      <c r="D14" t="n">
-        <v>8e-06</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8e-06</t>
+        </is>
       </c>
       <c r="E14" t="n">
         <v>2.39</v>
@@ -895,13 +921,13 @@
         <v>-20.74</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6723</v>
+        <v>0.67</v>
       </c>
       <c r="H14" t="n">
         <v>1.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9969</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -918,8 +944,10 @@
       <c r="C15" t="n">
         <v>6562.889</v>
       </c>
-      <c r="D15" t="n">
-        <v>1.2e-05</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1.2e-05</t>
+        </is>
       </c>
       <c r="E15" t="n">
         <v>3.53</v>
@@ -928,13 +956,13 @@
         <v>-20.4</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6605</v>
+        <v>0.66</v>
       </c>
       <c r="H15" t="n">
         <v>1.13</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9446</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -951,8 +979,10 @@
       <c r="C16" t="n">
         <v>6562.95</v>
       </c>
-      <c r="D16" t="n">
-        <v>2.1e-05</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2.1e-05</t>
+        </is>
       </c>
       <c r="E16" t="n">
         <v>6.3</v>
@@ -961,13 +991,13 @@
         <v>-20.2</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6398</v>
+        <v>0.64</v>
       </c>
       <c r="H16" t="n">
-        <v>1.174</v>
+        <v>1.17</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9154</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="17">
@@ -984,8 +1014,10 @@
       <c r="C17" t="n">
         <v>6562.93</v>
       </c>
-      <c r="D17" t="n">
-        <v>1.8e-05</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1.8e-05</t>
+        </is>
       </c>
       <c r="E17" t="n">
         <v>5.41</v>
@@ -994,13 +1026,13 @@
         <v>-22.24</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="H17" t="n">
-        <v>1.248</v>
+        <v>1.25</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0301</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="18">
@@ -1017,8 +1049,10 @@
       <c r="C18" t="n">
         <v>6562.96</v>
       </c>
-      <c r="D18" t="n">
-        <v>2.3e-05</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2.3e-05</t>
+        </is>
       </c>
       <c r="E18" t="n">
         <v>6.76</v>
@@ -1027,13 +1061,13 @@
         <v>-21.06</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6544</v>
+        <v>0.65</v>
       </c>
       <c r="H18" t="n">
-        <v>1.203</v>
+        <v>1.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9794</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="19">
@@ -1050,8 +1084,10 @@
       <c r="C19" t="n">
         <v>6562.994</v>
       </c>
-      <c r="D19" t="n">
-        <v>2.8e-05</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.8e-05</t>
+        </is>
       </c>
       <c r="E19" t="n">
         <v>8.31</v>
@@ -1060,13 +1096,13 @@
         <v>-21.18</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7407</v>
+        <v>0.74</v>
       </c>
       <c r="H19" t="n">
-        <v>1.259</v>
+        <v>1.26</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0243</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="20">
@@ -1083,8 +1119,10 @@
       <c r="C20" t="n">
         <v>6562.939</v>
       </c>
-      <c r="D20" t="n">
-        <v>1.9e-05</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1.9e-05</t>
+        </is>
       </c>
       <c r="E20" t="n">
         <v>5.8</v>
@@ -1093,13 +1131,13 @@
         <v>-23.71</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7325</v>
+        <v>0.73</v>
       </c>
       <c r="H20" t="n">
-        <v>1.324</v>
+        <v>1.32</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0691</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="21">
@@ -1116,8 +1154,10 @@
       <c r="C21" t="n">
         <v>6562.944</v>
       </c>
-      <c r="D21" t="n">
-        <v>2e-05</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2e-05</t>
+        </is>
       </c>
       <c r="E21" t="n">
         <v>6.01</v>
@@ -1126,13 +1166,13 @@
         <v>-22.95</v>
       </c>
       <c r="G21" t="n">
-        <v>0.716</v>
+        <v>0.72</v>
       </c>
       <c r="H21" t="n">
-        <v>1.297</v>
+        <v>1.3</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0139</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="22">
@@ -1149,8 +1189,10 @@
       <c r="C22" t="n">
         <v>6562.634</v>
       </c>
-      <c r="D22" t="n">
-        <v>-2.7e-05</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-2.7e-05</t>
+        </is>
       </c>
       <c r="E22" t="n">
         <v>-8.140000000000001</v>
@@ -1159,13 +1201,13 @@
         <v>-36.35</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8189</v>
+        <v>0.82</v>
       </c>
       <c r="H22" t="n">
-        <v>1.818</v>
+        <v>1.82</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6089</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="23">
@@ -1182,8 +1224,10 @@
       <c r="C23" t="n">
         <v>6562.719</v>
       </c>
-      <c r="D23" t="n">
-        <v>-1.4e-05</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-1.4e-05</t>
+        </is>
       </c>
       <c r="E23" t="n">
         <v>-4.23</v>
@@ -1192,13 +1236,13 @@
         <v>-30.81</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7935</v>
+        <v>0.79</v>
       </c>
       <c r="H23" t="n">
-        <v>1.612</v>
+        <v>1.61</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3921</v>
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción halpha 2024, 2025 y 2026.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción halpha 2024, 2025 y 2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -898,7 +898,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Julio 24-2026</t>
+          <t>Agosto 19-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -907,33 +907,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6562.864</v>
+        <v>6563.152</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8e-06</t>
+          <t>5.2e-05</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2.39</v>
+        <v>15.52</v>
       </c>
       <c r="F14" t="n">
-        <v>-20.74</v>
+        <v>-13.28</v>
       </c>
       <c r="G14" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Julio 27-2026</t>
+          <t>Julio 24-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -942,33 +942,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6562.889</v>
+        <v>6562.864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.2e-05</t>
+          <t>8e-06</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3.53</v>
+        <v>2.39</v>
       </c>
       <c r="F15" t="n">
-        <v>-20.4</v>
+        <v>-20.74</v>
       </c>
       <c r="G15" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="H15" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Agosto 06-2026</t>
+          <t>Julio 27-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -977,33 +977,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6562.95</v>
+        <v>6562.889</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.1e-05</t>
+          <t>1.2e-05</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6.3</v>
+        <v>3.53</v>
       </c>
       <c r="F16" t="n">
-        <v>-20.2</v>
+        <v>-20.4</v>
       </c>
       <c r="G16" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H16" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="I16" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Agosto 10-2026</t>
+          <t>Agosto 06-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1012,33 +1012,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6562.93</v>
+        <v>6562.95</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.8e-05</t>
+          <t>2.1e-05</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5.41</v>
+        <v>6.3</v>
       </c>
       <c r="F17" t="n">
-        <v>-22.24</v>
+        <v>-20.2</v>
       </c>
       <c r="G17" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="H17" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="I17" t="n">
-        <v>1.03</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Agosto 13-2026</t>
+          <t>Agosto 10-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1047,33 +1047,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6562.96</v>
+        <v>6562.93</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.3e-05</t>
+          <t>1.8e-05</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6.76</v>
+        <v>5.41</v>
       </c>
       <c r="F18" t="n">
-        <v>-21.06</v>
+        <v>-22.24</v>
       </c>
       <c r="G18" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="I18" t="n">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Agosto 28-2026</t>
+          <t>Agosto 13-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1082,33 +1082,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6562.994</v>
+        <v>6562.96</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.8e-05</t>
+          <t>2.3e-05</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.31</v>
+        <v>6.76</v>
       </c>
       <c r="F19" t="n">
-        <v>-21.18</v>
+        <v>-21.06</v>
       </c>
       <c r="G19" t="n">
-        <v>0.74</v>
+        <v>0.65</v>
       </c>
       <c r="H19" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="I19" t="n">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Septiembre 07-2026</t>
+          <t>Agosto 28-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1117,33 +1117,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6562.939</v>
+        <v>6562.994</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.9e-05</t>
+          <t>2.8e-05</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5.8</v>
+        <v>8.31</v>
       </c>
       <c r="F20" t="n">
-        <v>-23.71</v>
+        <v>-21.18</v>
       </c>
       <c r="G20" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="H20" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="I20" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Septiembre 14-2026</t>
+          <t>Septiembre 07-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1152,33 +1152,33 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6562.944</v>
+        <v>6562.939</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2e-05</t>
+          <t>1.9e-05</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6.01</v>
+        <v>5.8</v>
       </c>
       <c r="F21" t="n">
-        <v>-22.95</v>
+        <v>-23.71</v>
       </c>
       <c r="G21" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="I21" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Septiembre 21-2026</t>
+          <t>Septiembre 14-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1187,62 +1187,132 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6562.634</v>
+        <v>6562.944</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-2.7e-05</t>
+          <t>2e-05</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-8.140000000000001</v>
+        <v>6.01</v>
       </c>
       <c r="F22" t="n">
-        <v>-36.35</v>
+        <v>-22.95</v>
       </c>
       <c r="G22" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="H22" t="n">
-        <v>1.82</v>
+        <v>1.3</v>
       </c>
       <c r="I22" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Septiembre 21-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Absorción Hα</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>6562.634</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-2.7e-05</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>-8.140000000000001</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-36.35</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Septiembre 29-2026</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Absorción Hα</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Absorción Hα</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
         <v>6562.719</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>-1.4e-05</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="E24" t="n">
         <v>-4.23</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F24" t="n">
         <v>-30.81</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G24" t="n">
         <v>0.79</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H24" t="n">
         <v>1.61</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I24" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Octubre 16-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Absorción Hα</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>6562.575</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>-3.6e-05</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>-10.83</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-32.44</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>
